--- a/bench/results/jmeter_S1_analysis.xlsx
+++ b/bench/results/jmeter_S1_analysis.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\corey\Documents\GitHub\Honours-Project\bench\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B4D6FC-A6A5-4FBD-87E3-9974EE4653B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA1DDF8-F599-4CA8-B6D0-E35AB85A4512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3480" windowWidth="38640" windowHeight="21120" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,16 +342,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>175</c:v>
+                  <c:v>174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>160</c:v>
+                  <c:v>168</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>152</c:v>
+                  <c:v>163</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>151</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -429,16 +429,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>120</c:v>
+                  <c:v>180</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>83</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>82</c:v>
+                  <c:v>89</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>81</c:v>
+                  <c:v>87</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -516,16 +516,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>120</c:v>
+                  <c:v>272</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>128</c:v>
+                  <c:v>190</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>123</c:v>
+                  <c:v>192</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>125</c:v>
+                  <c:v>189</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -603,16 +603,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>67</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>55</c:v>
+                  <c:v>62</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>53</c:v>
+                  <c:v>65</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1083,16 +1083,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>175</c:v>
+                  <c:v>174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>201</c:v>
+                  <c:v>216</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>167</c:v>
+                  <c:v>179</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>168</c:v>
+                  <c:v>179</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1170,16 +1170,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>120</c:v>
+                  <c:v>186</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>95</c:v>
+                  <c:v>97</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>98</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>94</c:v>
+                  <c:v>102</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1257,16 +1257,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>120</c:v>
+                  <c:v>272</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>137</c:v>
+                  <c:v>199</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>137</c:v>
+                  <c:v>225</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>138</c:v>
+                  <c:v>208</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1344,16 +1344,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>67</c:v>
+                  <c:v>80</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>65</c:v>
+                  <c:v>72</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>69</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>67</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1834,16 +1834,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>175</c:v>
+                  <c:v>174</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>144</c:v>
+                  <c:v>155</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>149</c:v>
+                  <c:v>163</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>146</c:v>
+                  <c:v>152</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1921,16 +1921,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>120</c:v>
+                  <c:v>153</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>77</c:v>
+                  <c:v>85</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>77</c:v>
+                  <c:v>92</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>83</c:v>
+                  <c:v>88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1952,6 +1952,93 @@
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>Symfony</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Sheet1!$Y$3:$Y$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$AB$3:$AB$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>272</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>192</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>188</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-9880-4C67-8DB3-A8179AF9C323}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$AC$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Yii</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2003,108 +2090,21 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$AB$3:$AB$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>120</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>131</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>117</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>126</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-9880-4C67-8DB3-A8179AF9C323}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$AC$2</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Yii</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Sheet1!$Y$3:$Y$6</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>100</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
               <c:f>Sheet1!$AC$3:$AC$6</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>67</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56</c:v>
+                  <c:v>63</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>54</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2580,16 +2580,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>5.7142900000000001</c:v>
+                  <c:v>5.7471300000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0925400000000001</c:v>
+                  <c:v>1.0924199999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.01738</c:v>
+                  <c:v>1.0169999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.00867</c:v>
+                  <c:v>1.00851</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2667,16 +2667,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>8.3333300000000001</c:v>
+                  <c:v>0.80174999999999996</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1016900000000001</c:v>
+                  <c:v>1.10205</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.0189299999999999</c:v>
+                  <c:v>1.0186200000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0092000000000001</c:v>
+                  <c:v>1.00915</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2754,16 +2754,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>8.3333300000000001</c:v>
+                  <c:v>3.6764700000000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.09541</c:v>
+                  <c:v>1.0876699999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.01779</c:v>
+                  <c:v>1.0162599999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0087900000000001</c:v>
+                  <c:v>1.00813</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2841,16 +2841,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>14.925369999999999</c:v>
+                  <c:v>14.28571</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.1050899999999999</c:v>
+                  <c:v>1.10314</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.01912</c:v>
+                  <c:v>1.01885</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.0095400000000001</c:v>
+                  <c:v>1.0094000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3321,16 +3321,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>35</c:v>
+                  <c:v>39.950000000000003</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>36.5</c:v>
+                  <c:v>41.05</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>37.5</c:v>
+                  <c:v>41.05</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38.5</c:v>
+                  <c:v>41.35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3408,16 +3408,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>29.4</c:v>
+                  <c:v>35.5</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.4</c:v>
+                  <c:v>35.5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>30.5</c:v>
+                  <c:v>35.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>31</c:v>
+                  <c:v>35.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3495,16 +3495,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>30.5</c:v>
+                  <c:v>38</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32.6</c:v>
+                  <c:v>40.85</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>32.6</c:v>
+                  <c:v>40.85</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34</c:v>
+                  <c:v>40.85</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3582,16 +3582,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>28.9</c:v>
+                  <c:v>37.75</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>29.6</c:v>
+                  <c:v>37.75</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>29.8</c:v>
+                  <c:v>37.75</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>30.4</c:v>
+                  <c:v>37.75</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3799,7 +3799,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -7203,16 +7203,16 @@
         <v>1</v>
       </c>
       <c r="C3" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D3" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E3" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F3" s="2">
-        <v>5.7142900000000001</v>
+        <v>5.7471300000000003</v>
       </c>
       <c r="G3" s="3">
         <v>0</v>
@@ -7221,46 +7221,46 @@
         <v>1</v>
       </c>
       <c r="J3" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K3" s="2">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="L3" s="2">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="M3" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="Q3" s="2">
         <v>1</v>
       </c>
       <c r="R3" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S3" s="2">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="T3" s="2">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="U3" s="2">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="Y3" s="2">
         <v>1</v>
       </c>
       <c r="Z3" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AA3" s="2">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="AB3" s="2">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="AC3" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7271,16 +7271,16 @@
         <v>10</v>
       </c>
       <c r="C4" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="D4" s="2">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E4" s="2">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="F4" s="2">
-        <v>1.0925400000000001</v>
+        <v>1.0924199999999999</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -7289,46 +7289,46 @@
         <v>10</v>
       </c>
       <c r="J4" s="2">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="K4" s="2">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L4" s="2">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="M4" s="2">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="Q4" s="2">
         <v>10</v>
       </c>
       <c r="R4" s="2">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="S4" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="T4" s="2">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="U4" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="Y4" s="2">
         <v>10</v>
       </c>
       <c r="Z4" s="2">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="AA4" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AB4" s="2">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="AC4" s="2">
-        <v>56</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7339,16 +7339,16 @@
         <v>50</v>
       </c>
       <c r="C5" s="2">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="D5" s="2">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="E5" s="2">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="F5" s="2">
-        <v>1.01738</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="G5" s="3">
         <v>0</v>
@@ -7357,46 +7357,46 @@
         <v>50</v>
       </c>
       <c r="J5" s="2">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="K5" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L5" s="2">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="M5" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="Q5" s="2">
         <v>50</v>
       </c>
       <c r="R5" s="2">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="S5" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="T5" s="2">
-        <v>137</v>
+        <v>225</v>
       </c>
       <c r="U5" s="2">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="Y5" s="2">
         <v>50</v>
       </c>
       <c r="Z5" s="2">
-        <v>149</v>
+        <v>163</v>
       </c>
       <c r="AA5" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AB5" s="2">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="AC5" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7407,16 +7407,16 @@
         <v>100</v>
       </c>
       <c r="C6" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="D6" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="E6" s="2">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="F6" s="2">
-        <v>1.00867</v>
+        <v>1.00851</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -7425,46 +7425,46 @@
         <v>100</v>
       </c>
       <c r="J6" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K6" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L6" s="2">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="M6" s="2">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="Q6" s="2">
         <v>100</v>
       </c>
       <c r="R6" s="2">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="S6" s="2">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="T6" s="2">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="U6" s="2">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="Y6" s="2">
         <v>100</v>
       </c>
       <c r="Z6" s="2">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="AA6" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AB6" s="2">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="AC6" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7475,16 +7475,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="2">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="D7" s="2">
-        <v>120</v>
+        <v>153</v>
       </c>
       <c r="E7" s="2">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="F7" s="2">
-        <v>8.3333300000000001</v>
+        <v>0.80174999999999996</v>
       </c>
       <c r="G7" s="3">
         <v>0</v>
@@ -7498,16 +7498,16 @@
         <v>10</v>
       </c>
       <c r="C8" s="2">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D8" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E8" s="2">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F8" s="2">
-        <v>1.1016900000000001</v>
+        <v>1.10205</v>
       </c>
       <c r="G8" s="3">
         <v>0</v>
@@ -7521,16 +7521,16 @@
         <v>50</v>
       </c>
       <c r="C9" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="D9" s="2">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="E9" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F9" s="2">
-        <v>1.0189299999999999</v>
+        <v>1.0186200000000001</v>
       </c>
       <c r="G9" s="3">
         <v>0</v>
@@ -7544,16 +7544,16 @@
         <v>100</v>
       </c>
       <c r="C10" s="2">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D10" s="2">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="E10" s="2">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F10" s="2">
-        <v>1.0092000000000001</v>
+        <v>1.00915</v>
       </c>
       <c r="G10" s="3">
         <v>0</v>
@@ -7567,16 +7567,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="2">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="D11" s="2">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="E11" s="2">
-        <v>120</v>
+        <v>272</v>
       </c>
       <c r="F11" s="2">
-        <v>8.3333300000000001</v>
+        <v>3.6764700000000001</v>
       </c>
       <c r="G11" s="3">
         <v>0</v>
@@ -7590,16 +7590,16 @@
         <v>10</v>
       </c>
       <c r="C12" s="2">
-        <v>128</v>
+        <v>190</v>
       </c>
       <c r="D12" s="2">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="E12" s="2">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="F12" s="2">
-        <v>1.09541</v>
+        <v>1.0876699999999999</v>
       </c>
       <c r="G12" s="3">
         <v>0</v>
@@ -7613,16 +7613,16 @@
         <v>50</v>
       </c>
       <c r="C13" s="2">
-        <v>123</v>
+        <v>192</v>
       </c>
       <c r="D13" s="2">
-        <v>117</v>
+        <v>185</v>
       </c>
       <c r="E13" s="2">
-        <v>137</v>
+        <v>225</v>
       </c>
       <c r="F13" s="2">
-        <v>1.01779</v>
+        <v>1.0162599999999999</v>
       </c>
       <c r="G13" s="3">
         <v>0</v>
@@ -7636,16 +7636,16 @@
         <v>100</v>
       </c>
       <c r="C14" s="2">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="D14" s="2">
-        <v>126</v>
+        <v>188</v>
       </c>
       <c r="E14" s="2">
-        <v>138</v>
+        <v>208</v>
       </c>
       <c r="F14" s="2">
-        <v>1.0087900000000001</v>
+        <v>1.00813</v>
       </c>
       <c r="G14" s="3">
         <v>0</v>
@@ -7659,16 +7659,16 @@
         <v>1</v>
       </c>
       <c r="C15" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D15" s="2">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E15" s="2">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="F15" s="2">
-        <v>14.925369999999999</v>
+        <v>14.28571</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -7682,16 +7682,16 @@
         <v>10</v>
       </c>
       <c r="C16" s="2">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D16" s="2">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2">
-        <v>1.1050899999999999</v>
+        <v>1.10314</v>
       </c>
       <c r="G16" s="3">
         <v>0</v>
@@ -7705,16 +7705,16 @@
         <v>50</v>
       </c>
       <c r="C17" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D17" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="F17" s="2">
-        <v>1.01912</v>
+        <v>1.01885</v>
       </c>
       <c r="G17" s="3">
         <v>0</v>
@@ -7728,16 +7728,16 @@
         <v>100</v>
       </c>
       <c r="C18" s="2">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D18" s="2">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="F18" s="2">
-        <v>1.0095400000000001</v>
+        <v>1.0094000000000001</v>
       </c>
       <c r="G18" s="3">
         <v>0</v>
@@ -7788,31 +7788,31 @@
         <v>1</v>
       </c>
       <c r="J22" s="2">
-        <v>5.7142900000000001</v>
+        <v>5.7471300000000003</v>
       </c>
       <c r="K22" s="2">
-        <v>8.3333300000000001</v>
+        <v>0.80174999999999996</v>
       </c>
       <c r="L22" s="2">
-        <v>8.3333300000000001</v>
+        <v>3.6764700000000001</v>
       </c>
       <c r="M22" s="2">
-        <v>14.925369999999999</v>
+        <v>14.28571</v>
       </c>
       <c r="O22" s="7">
         <v>1</v>
       </c>
       <c r="P22" s="7">
-        <v>35</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="Q22" s="7">
-        <v>29.4</v>
+        <v>35.5</v>
       </c>
       <c r="R22" s="7">
-        <v>30.5</v>
+        <v>38</v>
       </c>
       <c r="S22" s="7">
-        <v>28.9</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="23" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7820,31 +7820,31 @@
         <v>10</v>
       </c>
       <c r="J23" s="2">
-        <v>1.0925400000000001</v>
+        <v>1.0924199999999999</v>
       </c>
       <c r="K23" s="2">
-        <v>1.1016900000000001</v>
+        <v>1.10205</v>
       </c>
       <c r="L23" s="2">
-        <v>1.09541</v>
+        <v>1.0876699999999999</v>
       </c>
       <c r="M23" s="2">
-        <v>1.1050899999999999</v>
+        <v>1.10314</v>
       </c>
       <c r="O23" s="7">
         <v>10</v>
       </c>
       <c r="P23" s="7">
-        <v>36.5</v>
+        <v>41.05</v>
       </c>
       <c r="Q23" s="7">
-        <v>29.4</v>
+        <v>35.5</v>
       </c>
       <c r="R23" s="7">
-        <v>32.6</v>
+        <v>40.85</v>
       </c>
       <c r="S23" s="7">
-        <v>29.6</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="24" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7852,31 +7852,31 @@
         <v>50</v>
       </c>
       <c r="J24" s="2">
-        <v>1.01738</v>
+        <v>1.0169999999999999</v>
       </c>
       <c r="K24" s="2">
-        <v>1.0189299999999999</v>
+        <v>1.0186200000000001</v>
       </c>
       <c r="L24" s="2">
-        <v>1.01779</v>
+        <v>1.0162599999999999</v>
       </c>
       <c r="M24" s="2">
-        <v>1.01912</v>
+        <v>1.01885</v>
       </c>
       <c r="O24" s="7">
         <v>50</v>
       </c>
       <c r="P24" s="7">
-        <v>37.5</v>
+        <v>41.05</v>
       </c>
       <c r="Q24" s="7">
-        <v>30.5</v>
+        <v>35.5</v>
       </c>
       <c r="R24" s="7">
-        <v>32.6</v>
+        <v>40.85</v>
       </c>
       <c r="S24" s="7">
-        <v>29.8</v>
+        <v>37.75</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7884,31 +7884,31 @@
         <v>100</v>
       </c>
       <c r="J25" s="2">
-        <v>1.00867</v>
+        <v>1.00851</v>
       </c>
       <c r="K25" s="2">
-        <v>1.0092000000000001</v>
+        <v>1.00915</v>
       </c>
       <c r="L25" s="2">
-        <v>1.0087900000000001</v>
+        <v>1.00813</v>
       </c>
       <c r="M25" s="2">
-        <v>1.0095400000000001</v>
+        <v>1.0094000000000001</v>
       </c>
       <c r="O25" s="7">
         <v>100</v>
       </c>
       <c r="P25" s="7">
-        <v>38.5</v>
+        <v>41.35</v>
       </c>
       <c r="Q25" s="7">
-        <v>31</v>
+        <v>35.5</v>
       </c>
       <c r="R25" s="7">
-        <v>34</v>
+        <v>40.85</v>
       </c>
       <c r="S25" s="7">
-        <v>30.4</v>
+        <v>37.75</v>
       </c>
     </row>
   </sheetData>

--- a/bench/results/jmeter_S1_analysis.xlsx
+++ b/bench/results/jmeter_S1_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Users\corey\Documents\GitHub\Honours-Project\bench\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCA1DDF8-F599-4CA8-B6D0-E35AB85A4512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FDBFB08-30CE-44E8-A765-9338BE0FF784}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-3480" windowWidth="38640" windowHeight="21120" tabRatio="117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
